--- a/reports/一级子公司A_利润表_2026-10.xlsx
+++ b/reports/一级子公司A_利润表_2026-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>184668091</v>
+        <v>188935823</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>179912795</v>
+        <v>180055076</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1720520204</v>
+        <v>1720068802</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>733634</v>
+        <v>739245</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7115114</v>
+        <v>7120571</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>638060</v>
+        <v>641370</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6173900</v>
+        <v>6179901</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>542033</v>
+        <v>543031</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5233171</v>
+        <v>5237871</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>497121</v>
+        <v>498773</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4813824</v>
+        <v>4818604</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>269802</v>
+        <v>270483</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2615809</v>
+        <v>2618197</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>216618</v>
+        <v>215911</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2093058</v>
+        <v>2093801</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>181770823</v>
+        <v>186027010</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>177015527</v>
+        <v>177146263</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>91375224</v>
+        <v>90875435</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>842239521</v>
+        <v>841919042</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1678533</v>
+        <v>1667480</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>16221590</v>
+        <v>16204567</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1514366</v>
+        <v>1509255</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>14651668</v>
+        <v>14635630</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>80647650</v>
+        <v>81260803</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>801889308</v>
+        <v>801748554</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1732471</v>
+        <v>1735248</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>16743320</v>
+        <v>16740073</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>759401</v>
+        <v>759841</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7326926</v>
+        <v>7325615</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2696350</v>
+        <v>2718593</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>26159968</v>
+        <v>26180399</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1187333</v>
+        <v>1195901</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>11509493</v>
+        <v>11519489</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4659912</v>
+        <v>4673911</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>45002630</v>
+        <v>45041380</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>95384</v>
+        <v>93057</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>935357</v>
+        <v>928054</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2470422</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>23881966</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1643357</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>15916927</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>127792076</v>
+        <v>136327450</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>114634720</v>
+        <v>114334026</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>112360493</v>
+        <v>112074768</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1064887422</v>
+        <v>1064492326</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2274227</v>
+        <v>2259258</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>21976816</v>
+        <v>21957203</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4091867</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>39725103</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1311511</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>12712449</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>821410</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>7946940</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>987863</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>9539656</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>742323</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>7157797</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>495530</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4773915</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>413135</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3979684</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1897836</v>
+        <v>1901673</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>18316742</v>
+        <v>18331627</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1457992</v>
+        <v>1465095</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>14127079</v>
+        <v>14142137</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1187110</v>
+        <v>1191663</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>11509418</v>
+        <v>11521812</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8994818</v>
+        <v>8971755</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>86864937</v>
+        <v>86912051</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>371294</v>
+        <v>377584</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3638426</v>
+        <v>3663627</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>706298</v>
+        <v>687110</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6957944</v>
+        <v>6898700</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>802906</v>
+        <v>687110</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>7893079</v>
+        <v>6898700</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>95522</v>
+        <v>92221</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>935365</v>
+        <v>926056</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>350793</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3518591</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>717417</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6952246</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>234758</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2346608</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176453</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1760680</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>294637</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2935868</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1032472</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>9946186</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>157384</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1567055</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117970</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1175514</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>196342</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1959170</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>137169</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1371140</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97761</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>979027</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>78048</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>782863</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58447</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>586871</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>53978747</v>
+        <v>52193817</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63292426</v>
+        <v>58949597</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>409336</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3972475</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>97634</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>977507</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>159047</v>
+        <v>154485</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1558387</v>
+        <v>1543885</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>53819700</v>
+        <v>52448668</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5587995</v>
+        <v>5480277</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>55042867</v>
+        <v>54600130</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48231705</v>
+        <v>46968391</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48231705</v>
+        <v>46968391</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48231705</v>
+        <v>46968391</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48231705</v>
+        <v>46968391</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48231705</v>
+        <v>46968391</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
